--- a/项目阶段进度表.xlsx
+++ b/项目阶段进度表.xlsx
@@ -1,282 +1,185 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\AppData\Local\Kingsoft\WPS Office\12.1.0.28488\office6\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="30720" windowHeight="13380" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
-  <si>
-    <t>阶段</t>
-  </si>
-  <si>
-    <t>状态</t>
-  </si>
-  <si>
-    <t>依据</t>
-  </si>
-  <si>
-    <t>需求分析</t>
-  </si>
-  <si>
-    <t>仍缺正式SRS</t>
-  </si>
-  <si>
-    <t>只有《用户评分.txt》评审意见，功能边界/兼容性矩阵未成文</t>
-  </si>
-  <si>
-    <t>架构设计与选型</t>
-  </si>
-  <si>
-    <t>主体完成</t>
-  </si>
-  <si>
-    <t>v3架构7层+横切+4个关键机制已规格化并落进P1代码</t>
-  </si>
-  <si>
-    <t>详细设计</t>
-  </si>
-  <si>
-    <t>部分完成</t>
-  </si>
-  <si>
-    <t>contracts包（enums/models/errors/stable_id/state_hash/validators）已在P1落地</t>
-  </si>
-  <si>
-    <t>编码实现</t>
-  </si>
-  <si>
-    <t>当前所在</t>
-  </si>
-  <si>
-    <t>P1完成：6项验收全☑，env_adapter在真实环境冒烟通过</t>
-  </si>
-  <si>
-    <t>测试</t>
-  </si>
-  <si>
-    <t>起步</t>
-  </si>
-  <si>
-    <t>P1有3个单测文件（8+6+13用例）；集成/系统测试未开始</t>
-  </si>
-  <si>
-    <t>部署上线</t>
-  </si>
-  <si>
-    <t>未开始</t>
-  </si>
-  <si>
-    <t>分发形态未定（但打包工具链已确认可用）</t>
-  </si>
-  <si>
-    <t>运维迭代</t>
-  </si>
-  <si>
-    <t>观测设计已写未落地</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="21">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <b val="1"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -606,176 +509,177 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1021,7 +925,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1030,7 +934,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1043,11 +947,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1299,130 +1266,223 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="53.5555555555556" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="53.5555555555556" defaultRowHeight="14.4" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="8.77777777777778" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7777777777778" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7777777777778" style="1" customWidth="1"/>
-    <col min="4" max="4" width="92.1203703703704" style="1" customWidth="1"/>
-    <col min="5" max="16383" width="53.5555555555556" style="1" customWidth="1"/>
-    <col min="16384" max="16384" width="53.5555555555556" style="1"/>
+    <col width="8.77777777777778" customWidth="1" style="1" min="1" max="1"/>
+    <col width="14.7777777777778" customWidth="1" style="1" min="2" max="2"/>
+    <col width="27.7777777777778" customWidth="1" style="1" min="3" max="3"/>
+    <col width="92.1203703703704" customWidth="1" style="1" min="4" max="4"/>
+    <col width="92.1203703703704" customWidth="1" style="1" min="5" max="16383"/>
+    <col width="92.1203703703704" customWidth="1" style="7" min="6" max="6"/>
+    <col width="53.5555555555556" customWidth="1" style="1" min="16384" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1">
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>阶段</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>依据</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>验收</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>遗留</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>需求分析</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>仍缺正式SRS</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>只有《用户评分.txt》评审意见，功能边界/兼容性矩阵未成文</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>架构设计与选型</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>主体完成</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>v3架构7层+横切+4个关键机制已规格化并落进P1代码</t>
+        </is>
+      </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="s">
+    <row r="4">
+      <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>详细设计</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>部分完成</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>contracts包（enums/models/errors/stable_id/state_hash/validators）已在P1落地</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>编码实现</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>当前所在</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>P1完成：6项验收全☑，env_adapter在真实环境冒烟通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>起步</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>P1有3个单测文件（8+6+13用例）；集成/系统测试未开始</t>
+        </is>
+      </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
+    <row r="7">
+      <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>部署上线</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>分发形态未定（但打包工具链已确认可用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>运维迭代</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>观测设计已写未落地</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="4">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="4">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="4">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>22</v>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>P1 契约+适配</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>完成日期：2026-09-16 22:19；P1 验收证据与 MIGRATION.md 已封板</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>56 测试通过 + pyc 备份（12834 个）+ tag ui-toolbox-P1-20260916</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>ocr/sendinput 的 P2 契约化</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>